--- a/mapping/npc_gifttransaction_from_opportunity.xlsx
+++ b/mapping/npc_gifttransaction_from_opportunity.xlsx
@@ -443,6 +443,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>Exact name match (normalized). Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1516,7 +1517,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1586,7 +1587,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("005fj00000J30tNAAR") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 100.0% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2741,7 +2742,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No confident match found -- needs manual review. Also: Only 16.7% populated, and every populated row has the same value ("a09fj00000IzYdVAAV") -- no differentiating information, likely not worth migrating.</t>
+          <t>No confident match found -- needs manual review. Also: Only 16.7% populated, and every populated row has the same value ("&lt;SAMPLE_ID_REDACTED&gt;") -- no differentiating information, likely not worth migrating.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
